--- a/test/generator/baseline/gen.pdf.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pdf.to.xlsx.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Tables 4" sheetId="4" r:id="rId4"/>
     <sheet name="Tables 5" sheetId="5" r:id="rId5"/>
     <sheet name="Text" sheetId="6" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -325,8 +326,10 @@
       <c r="C3">
         <v>103</v>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -364,8 +367,10 @@
       <c r="C6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>4</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -966,198 +971,226 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">i Endnotes are typically used for longer notes, they remain endnotes when converted into ebook form, except that they have an additional backlink to make it easy to return to the current position after reading the note.</t>
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lists</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lists</t>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All types of lists are supported by the conversion, with the exception of lists that use fancy bullets, these get converted to regular bullets.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">All types of lists are supported by the conversion, with the exception of lists that use fancy bullets, these get converted to regular bullets.</t>
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulleted List</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulleted List</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Two</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two</t>
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numbered List</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numbered List</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
+          <t xml:space="preserve">Two</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two</t>
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-level Lists</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Multi-level Lists</t>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Two</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">Three</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three</t>
+          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
+          <t xml:space="preserve">Five</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">Six</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six</t>
+          <t xml:space="preserve">A Multi-level list with bullets:</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Multi-level list with bullets:</t>
+          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Two</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
+          <t xml:space="preserve">Four</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">Five</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Five</t>
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continued Lists</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Continued Lists</t>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Two</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
+          <t xml:space="preserve">We now resume our normal programming</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">We now resume our normal programming</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
           <t xml:space="preserve">Four</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footnote 1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In paged media, footnotes are usually displayed at the bottom of the text. However, in ebooks, a better paradigm is to make them clickable endnotes that the user can browse at her pleasure. This conversion is handled automatically by calibre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footnote 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i Endnotes are typically used for longer notes, they remain endnotes when converted into ebook form, except that they have an additional backlink to make it easy to return to the current position after reading the note.</t>
         </is>
       </c>
     </row>

--- a/test/generator/baseline/gen.pdf.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pdf.to.xlsx.xlsx
@@ -777,7 +777,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footnotes1 and endnotesi are automatically recognized and both are converted to endnotes, with backlinks for maximum ease of use in ebook devices.</t>
+          <t xml:space="preserve">Footnotes1 and endnotesi are automatically recognized and both are converted to endnotes, with backlinks for maximum ease of use in ebook devices. [Footnote 1]</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
@@ -1015,14 +1015,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
+          <t xml:space="preserve">1. One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">2. Two</t>
         </is>
       </c>
     </row>
@@ -1036,42 +1036,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1.1. Two</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three</t>
+          <t xml:space="preserve">1.1.1. Three</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
+          <t xml:space="preserve">1.1.2. Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">1.1.3. Five</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six</t>
+          <t xml:space="preserve">2. Six</t>
         </is>
       </c>
     </row>
@@ -1085,35 +1085,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">▪ One</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
+          <t xml:space="preserve">• This bullet uses an image as the bullet item</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">o Four</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">▪ Five</t>
         </is>
       </c>
     </row>
@@ -1127,14 +1127,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">i. One</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">ii. Two</t>
         </is>
       </c>
     </row>
@@ -1148,14 +1148,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">We now resume our normal programming</t>
+          <t xml:space="preserve">iii. We now resume our normal programming</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">iv. Four</t>
         </is>
       </c>
     </row>

--- a/test/generator/baseline/gen.pdf.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pdf.to.xlsx.xlsx
@@ -1160,6 +1160,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A31" r:id="rId1"/>
+  </hyperlinks>
 </worksheet>
 </file>
 

--- a/test/generator/baseline/gen.pdf.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pdf.to.xlsx.xlsx
@@ -1162,6 +1162,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A31" r:id="rId1"/>
+    <hyperlink ref="A39" location="Tables!A1"/>
   </hyperlinks>
 </worksheet>
 </file>
